--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,22 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>ستينج فراولة مينى تربو - 250 مل</t>
-  </si>
-  <si>
-    <t>شاى الكبوس ناعم - 30 جم</t>
-  </si>
-  <si>
-    <t>راني عصير مشروب خوخ - 235 مل</t>
-  </si>
-  <si>
-    <t>بيج كولا  ليمون- 200 مل</t>
-  </si>
-  <si>
-    <t>بيج كولا ليمون - 360 مل</t>
-  </si>
-  <si>
-    <t>بيج كولا برتقال - 360 مل</t>
+    <t>هيركود شامبو اكياس حماية يوميه بالليمون - 5 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -413,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,121 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6158</v>
+        <v>24252</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>9082</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1762.5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>9082</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>11.75</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>11288</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>316</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>11390</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>135</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23261</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>98.5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23262</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>98.75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>هيركود شامبو اكياس حماية يوميه بالليمون - 5 مل</t>
+    <t>صلصة دهشة ظرف - 35 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24252</v>
+        <v>5086</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,9 +435,26 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>5086</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>42.75</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>Product ID</t>
   </si>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>صلصة دهشة ظرف - 35 جم</t>
+  </si>
+  <si>
+    <t>بسكويت بسكاتو بامبى - 3 جنية</t>
+  </si>
+  <si>
+    <t>مسحوق باهي يدوي لافندر  - 60 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,10 +441,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -452,10 +458,61 @@
         <v>3</v>
       </c>
       <c r="D3">
-        <v>42.75</v>
+        <v>45.5</v>
       </c>
       <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>10666</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>240</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>10666</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24567</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>صلصة دهشة ظرف - 35 جم</t>
-  </si>
-  <si>
-    <t>بسكويت بسكاتو بامبى - 3 جنية</t>
-  </si>
-  <si>
-    <t>مسحوق باهي يدوي لافندر  - 60 جم</t>
+    <t>صابون ريفولى - 110 جم</t>
+  </si>
+  <si>
+    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
+  </si>
+  <si>
+    <t>حلوانى مربى مشمش- 700 جم</t>
+  </si>
+  <si>
+    <t>شامبو وبسلم سباركل للشعر العادي - 350 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,7 +435,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>5086</v>
+        <v>1309</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -441,78 +444,112 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>182</v>
+        <v>534</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>5086</v>
+        <v>1309</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>10666</v>
+        <v>2424</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>240</v>
+        <v>865</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>10666</v>
+        <v>2424</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D5">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24567</v>
+        <v>2508</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>753.75</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>6034</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>43.25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>6034</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
+      <c r="D8">
+        <v>1038</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>صابون ريفولى - 110 جم</t>
-  </si>
-  <si>
-    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
-  </si>
-  <si>
-    <t>حلوانى مربى مشمش- 700 جم</t>
-  </si>
-  <si>
-    <t>شامبو وبسلم سباركل للشعر العادي - 350 مل</t>
+    <t>بيبسى - 2.43 لتر</t>
+  </si>
+  <si>
+    <t>مناديل فاميليا تواليت مضغوط 5 رول + 1 رول هدية - 6 رول</t>
+  </si>
+  <si>
+    <t>مكرونة شعرية كايرو - 400 جم</t>
+  </si>
+  <si>
+    <t>مكرونة كايرو مرمرية - 400 جم</t>
+  </si>
+  <si>
+    <t>جبنة لا فاش كيرى كلاسيك - 8 مثلث</t>
+  </si>
+  <si>
+    <t>كوكا كولا كانز ستار - 320 مل</t>
+  </si>
+  <si>
+    <t>فرسكا شوكو بار حلاوة12 قطعه حجم اكبر 5 جنية</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,121 +444,155 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1309</v>
+        <v>589</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>534</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1309</v>
+        <v>3442</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>44.5</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>2424</v>
+        <v>5849</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>865</v>
+        <v>186.25</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>2424</v>
+        <v>5850</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>173</v>
+        <v>186.5</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>2508</v>
+        <v>10149</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>753.75</v>
+        <v>1240</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>6034</v>
+        <v>10149</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>43.25</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>6034</v>
+        <v>11396</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>335</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>12588</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>52.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>12588</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D8">
-        <v>1038</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="D10">
+        <v>630</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,31 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بيبسى - 2.43 لتر</t>
-  </si>
-  <si>
-    <t>مناديل فاميليا تواليت مضغوط 5 رول + 1 رول هدية - 6 رول</t>
-  </si>
-  <si>
-    <t>مكرونة شعرية كايرو - 400 جم</t>
-  </si>
-  <si>
-    <t>مكرونة كايرو مرمرية - 400 جم</t>
-  </si>
-  <si>
-    <t>جبنة لا فاش كيرى كلاسيك - 8 مثلث</t>
-  </si>
-  <si>
-    <t>كوكا كولا كانز ستار - 320 مل</t>
-  </si>
-  <si>
-    <t>فرسكا شوكو بار حلاوة12 قطعه حجم اكبر 5 جنية</t>
+    <t>كوكا كولا جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>سبرايت جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>فانتا برتقال جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>شويبس جولد خوخ جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>كوكا كولا تربو زيرو - 300 مل</t>
+  </si>
+  <si>
+    <t>أمريكانا فول سادة 20% خصم-( 12عرض*2عبوة ) 400 جم</t>
+  </si>
+  <si>
+    <t>فاين ديل مناديل وجه 380 منديل *2 طبقة عبوة التوفير 380 منديل</t>
+  </si>
+  <si>
+    <t>مشروب بودرة تانج مانجو جديد 2 لتر - 40 جرام</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,7 +450,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -453,49 +459,49 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>3442</v>
+        <v>616</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>5849</v>
+        <v>624</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>186.25</v>
+        <v>291.75</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>5850</v>
+        <v>2879</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -504,95 +510,129 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>186.5</v>
+        <v>785</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>10149</v>
+        <v>5494</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>1240</v>
+        <v>292</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>10149</v>
+        <v>11454</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>76.75</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>11396</v>
+        <v>13118</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>335</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>12588</v>
+        <v>13118</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>431</v>
       </c>
       <c r="D9">
-        <v>52.5</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>12588</v>
+        <v>13266</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>262.75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24127</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>120.75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24127</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D10">
-        <v>630</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
+      <c r="D12">
+        <v>1207.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,31 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوكا كولا جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>سبرايت جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>فانتا برتقال جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>شويبس جولد خوخ جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>كوكا كولا تربو زيرو - 300 مل</t>
-  </si>
-  <si>
-    <t>أمريكانا فول سادة 20% خصم-( 12عرض*2عبوة ) 400 جم</t>
-  </si>
-  <si>
-    <t>فاين ديل مناديل وجه 380 منديل *2 طبقة عبوة التوفير 380 منديل</t>
-  </si>
-  <si>
-    <t>مشروب بودرة تانج مانجو جديد 2 لتر - 40 جرام</t>
+    <t>ميني كتاكيتو بالشوكولاتة  - 10 ج</t>
+  </si>
+  <si>
+    <t>سلايت زيت عباد الشمس مكرر- 675 مل</t>
+  </si>
+  <si>
+    <t>زيت عافية ذرة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>فانتا تفاح احمر ستار - 320 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -422,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -450,189 +435,87 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>615</v>
+        <v>975</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>96.5</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>616</v>
+        <v>975</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>290</v>
+        <v>1158</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>624</v>
+        <v>1082</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>291.75</v>
+        <v>709.5</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>2879</v>
+        <v>2538</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>785</v>
+        <v>881</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>5494</v>
+        <v>3671</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>11454</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>76.75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>13118</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>408</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>13118</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>431</v>
-      </c>
-      <c r="D9">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>13266</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>262.75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24127</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>120.75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24127</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1207.5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>الحمد جبنة موتزاريلا البيضاء - 400 جم</t>
-  </si>
-  <si>
-    <t>الحمد جبنة موتزاريلا البيضاء - 1 كجم</t>
-  </si>
-  <si>
-    <t>ريحانة  بقسماط ناعم - 300 جم</t>
+    <t>سمنة حبوبة نباتى صفراء - 300 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6395</v>
+        <v>11403</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -441,95 +435,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1325</v>
+        <v>360.5</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>6395</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>6396</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>6396</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1260</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>7673</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>7673</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>360</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>سمنة حبوبة نباتى صفراء - 300 جم</t>
+    <t>أطياب صدور بانية عادى - 400 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,18 +426,35 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>11403</v>
+        <v>6339</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>112.25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>6339</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>360.5</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D3">
+        <v>2694</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>أطياب صدور بانية عادى - 400 جم</t>
+    <t>مكرونة الملكة فرن - 400 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,35 +426,18 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6339</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>112.25</v>
+        <v>259.25</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>6339</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2694</v>
-      </c>
-      <c r="E3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>مكرونة الملكة فرن - 400 جم</t>
+    <t>حلو الشام رايت شيف جديد - 18 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>25</v>
+        <v>13326</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,9 +435,26 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>259.25</v>
+        <v>498</v>
       </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>13326</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>41.5</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="32">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,76 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>حلو الشام رايت شيف جديد - 18 جم</t>
+    <t>شهرزاد بامية زيرو - 400 جم</t>
+  </si>
+  <si>
+    <t>شهرزاد بامية ممتازة - 400 جم</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 8 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مثلثات - 16 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة كريمى  بالقشطة - 4 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية جبنة مربعات ب القشطة - 6 قطعه</t>
+  </si>
+  <si>
+    <t>باندا جورمية مربعات جبنة بالقشطة - 8 قطعه</t>
+  </si>
+  <si>
+    <t>جبنة باندا فيتا  - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا رومى - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنة باندا بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس  - 125 جم</t>
+  </si>
+  <si>
+    <t>جبنة ديرى فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>جوتيلا مكس كريمة الشوكولاتة بالبندق والشوكولاتة البيضاء - 18 جم</t>
+  </si>
+  <si>
+    <t>جوتيلا كاكاو بودر خام - 80 جم</t>
+  </si>
+  <si>
+    <t>جوتيلا جولد كريمة البندق بالشوكولاتة %20 بنـدق - 350 جم</t>
+  </si>
+  <si>
+    <t>عرض باندا ( 2علبة باندا250 جم + علبة فول باندا 400جم) - 900 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,36 +495,665 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>13326</v>
+        <v>7523</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>498</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>13326</v>
+        <v>7523</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>680</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>7523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>340</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>7523</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>8139</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>210</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>8139</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>420</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>8139</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>8139</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21704</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1386</v>
+      </c>
+      <c r="E10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21704</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>41.5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
+      <c r="D11">
+        <v>38.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21705</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1740</v>
+      </c>
+      <c r="E12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21705</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>72.5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21706</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14">
+        <v>26.75</v>
+      </c>
+      <c r="E14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21706</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>963</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21707</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1272</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>21707</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>53</v>
+      </c>
+      <c r="E17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>21708</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>21708</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>2080</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>21709</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1132.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>21709</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>37.75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21710</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>21710</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>2940</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>21745</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>417.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>21752</v>
+      </c>
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>474.25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>21754</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>417.5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>21771</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>417.5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>21773</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>368.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>21774</v>
+      </c>
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>474.25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>21777</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>368.5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>21778</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>474.25</v>
+      </c>
+      <c r="E31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>21779</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>417.5</v>
+      </c>
+      <c r="E32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>21781</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>283</v>
+      </c>
+      <c r="E33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>21789</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>310</v>
+      </c>
+      <c r="E34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>24978</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>100</v>
+      </c>
+      <c r="E35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>24978</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>600</v>
+      </c>
+      <c r="E36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>24979</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>62.5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>24979</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>750</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>25632</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>2150</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>25775</v>
+      </c>
+      <c r="B40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>280</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,67 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>نوفي فينجرز شيكولاتة بيضاء - 5 جنية</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>هنادى زيت خليط- 2.1 لتر</t>
+  </si>
+  <si>
+    <t>هدية زيت خليط- 0.7 لتر</t>
+  </si>
+  <si>
+    <t>سلايت زيت عباد الشمس مكرر- 675 مل</t>
+  </si>
+  <si>
+    <t>سلايت زيت عباد الشمس- 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 2.25 لتر</t>
+  </si>
+  <si>
+    <t>زيت ذرة ريحانة بيور - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت عافية عباد الشمس - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت عافية ذرة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +486,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21687</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,27 +495,350 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>297</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21687</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>24.75</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>823</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>764.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>856</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>869</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>858</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>605</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>924</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>612</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>1082</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>715</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>1084</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>716</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>1091</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>655</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>1447</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>754.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>1490</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>604</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>1492</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>860</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>2916</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>955</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>4203</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>640</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>6497</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>855</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>9358</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>554</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>12661</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>387</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>12662</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>475</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>12923</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>855</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>12924</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>600</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>12925</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>490</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,67 +37,52 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+    <t>زيت قلية خليط - 2.1 لتر</t>
   </si>
   <si>
     <t>زيت حبوبة خليط - 900 مل</t>
   </si>
   <si>
-    <t>زيت حلوة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>هنادى زيت خليط- 2.1 لتر</t>
-  </si>
-  <si>
-    <t>هدية زيت خليط- 0.7 لتر</t>
-  </si>
-  <si>
-    <t>سلايت زيت عباد الشمس مكرر- 675 مل</t>
-  </si>
-  <si>
-    <t>سلايت زيت عباد الشمس- 2.1 لتر</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 2.25 لتر</t>
-  </si>
-  <si>
-    <t>زيت ذرة ريحانة بيور - 700 مل</t>
+    <t>جبنة دومتى فيتا بلس - 125 جم</t>
   </si>
   <si>
     <t>زيت حبوبة خليط - 700 مل</t>
   </si>
   <si>
-    <t>زيت حبوبة خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>زيت حلوة خليط - 4.5 لتر</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 1.8 لتر</t>
-  </si>
-  <si>
-    <t>زيت عافية عباد الشمس - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت عافية ذرة - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 1 لتر</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>زيت ثمرات خليط - 550 مل</t>
+    <t>سندة زيت خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 2.4 لتر</t>
+  </si>
+  <si>
+    <t>جبنة دومتى فيتا بلس زيتون - 125 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بالزيتون  - 250 مل</t>
+  </si>
+  <si>
+    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بسطرمة - 250 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس رومي - 500 جم</t>
+  </si>
+  <si>
+    <t>دومتي جبنة فيتا بلس شيدر - 250 جم</t>
+  </si>
+  <si>
+    <t>جبنه دومتى جولد -- 250 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -458,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -486,7 +471,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>9</v>
+        <v>471</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -495,15 +480,15 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>866</v>
+        <v>612.25</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>448</v>
+        <v>823</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -512,15 +497,15 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>777</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>823</v>
+        <v>903</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -529,15 +514,15 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>764.5</v>
+        <v>402</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>856</v>
+        <v>1490</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -546,15 +531,15 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>869</v>
+        <v>620</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>858</v>
+        <v>6496</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -563,15 +548,15 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>605</v>
+        <v>772</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>924</v>
+        <v>11402</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -580,15 +565,15 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>612</v>
+        <v>717</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>1082</v>
+        <v>13210</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -597,248 +582,163 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>715</v>
+        <v>402</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>1084</v>
+        <v>19980</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>716</v>
+        <v>519</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>1091</v>
+        <v>19981</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>655</v>
+        <v>460</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>1447</v>
+        <v>19982</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>754.5</v>
+        <v>519</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>1490</v>
+        <v>19985</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>604</v>
+        <v>460</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>1492</v>
+        <v>19988</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>860</v>
+        <v>519</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>2916</v>
+        <v>19989</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>955</v>
+        <v>460</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>4203</v>
+        <v>19991</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>640</v>
+        <v>460</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>6497</v>
+        <v>19992</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>855</v>
+        <v>519</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>9358</v>
+        <v>26103</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>554</v>
+        <v>654</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>12661</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>387</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>12662</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>475</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>12923</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>855</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>12924</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>600</v>
-      </c>
-      <c r="E21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>12925</v>
-      </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>490</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,52 +37,31 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>زيت قلية خليط - 2.1 لتر</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس - 125 جم</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 700 مل</t>
-  </si>
-  <si>
-    <t>سندة زيت خليط - 900 مل</t>
-  </si>
-  <si>
-    <t>زيت حبوبة خليط - 2.4 لتر</t>
-  </si>
-  <si>
-    <t>جبنة دومتى فيتا بلس زيتون - 125 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بالزيتون  - 250 مل</t>
-  </si>
-  <si>
-    <t>دومتي جبنة اسطنبولي بلس - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 250 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس بسطرمة - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس رومي - 500 جم</t>
-  </si>
-  <si>
-    <t>دومتي جبنة فيتا بلس شيدر - 250 جم</t>
-  </si>
-  <si>
-    <t>جبنه دومتى جولد -- 250 جم</t>
+    <t>صابون كامى اناقة -- 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى حيوية - 110 جم</t>
+  </si>
+  <si>
+    <t>صابون كامى رومانسية - 110 جم</t>
+  </si>
+  <si>
+    <t>لوكس صابون حلم السعادة  - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة مثالية - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 115 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس بشرة نضرة - 165 جم</t>
+  </si>
+  <si>
+    <t>صابون لوكس سحر الاوركيد - 165 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -443,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -471,274 +450,308 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>471</v>
+        <v>8283</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>612.25</v>
+        <v>60.5</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>823</v>
+        <v>8283</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>777</v>
+        <v>726</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>903</v>
+        <v>8284</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>402</v>
+        <v>60.5</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>1490</v>
+        <v>8284</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>620</v>
+        <v>726</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>6496</v>
+        <v>8286</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>772</v>
+        <v>60.5</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>11402</v>
+        <v>8286</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>717</v>
+        <v>726</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>13210</v>
+        <v>9065</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>402</v>
+        <v>94.25</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19980</v>
+        <v>9065</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>519</v>
+        <v>754</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19981</v>
+        <v>11687</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>460</v>
+        <v>94.25</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19982</v>
+        <v>11687</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>519</v>
+        <v>754</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19985</v>
+        <v>11689</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>460</v>
+        <v>94.25</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19988</v>
+        <v>11689</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>519</v>
+        <v>754</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19989</v>
+        <v>11690</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>460</v>
+        <v>94.25</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19991</v>
+        <v>11690</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>460</v>
+        <v>754</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19992</v>
+        <v>11885</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>519</v>
+        <v>152.5</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>26103</v>
+        <v>11885</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>654</v>
+        <v>1220</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>11886</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>152.5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>11886</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1220</v>
+      </c>
+      <c r="E19" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/uploads/module_4_700.xlsx
+++ b/Pricing Logic/modules/uploads/module_4_700.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,31 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>صابون كامى اناقة -- 110 جم</t>
-  </si>
-  <si>
-    <t>صابون كامى حيوية - 110 جم</t>
-  </si>
-  <si>
-    <t>صابون كامى رومانسية - 110 جم</t>
-  </si>
-  <si>
-    <t>لوكس صابون حلم السعادة  - 115 جم</t>
-  </si>
-  <si>
-    <t>صابون لوكس بشرة مثالية - 115 جم</t>
-  </si>
-  <si>
-    <t>صابون لوكس بشرة نضرة - 115 جم</t>
-  </si>
-  <si>
-    <t>صابون لوكس سحر الاوركيد - 115 جم</t>
-  </si>
-  <si>
-    <t>صابون لوكس بشرة نضرة - 165 جم</t>
-  </si>
-  <si>
-    <t>صابون لوكس سحر الاوركيد - 165 جم</t>
+    <t>سمن كريستال ابيض صفيحة - 4.25 كجم</t>
   </si>
   <si>
     <t>YES</t>
@@ -422,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -450,308 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>8283</v>
+        <v>4926</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>60.5</v>
+        <v>388.75</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>8283</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>726</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>8284</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>60.5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>8284</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>726</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>8286</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>60.5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>8286</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>726</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>9065</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>94.25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>9065</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>754</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>11687</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>94.25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>11687</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>754</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>11689</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>94.25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>11689</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>754</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>11690</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>94.25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>11690</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>754</v>
-      </c>
-      <c r="E15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>11885</v>
-      </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>152.5</v>
-      </c>
-      <c r="E16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>11885</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1220</v>
-      </c>
-      <c r="E17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>11886</v>
-      </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>152.5</v>
-      </c>
-      <c r="E18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>11886</v>
-      </c>
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1220</v>
-      </c>
-      <c r="E19" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
